--- a/excel_project/部门考勤数据/空运部 (Air Freight)_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/空运部 (Air Freight)_异常考勤数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>侯杰-Willis Hou</t>
+          <t>顾丹妮-Dannie Gu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-10-13 星期一</t>
+          <t>25-10-27 星期一</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>叶楠</t>
+          <t>顾丹妮-Dannie Gu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,27 +515,101 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25-09-22 星期一</t>
+          <t>25-11-11 星期二</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>补卡审批通过</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>21:56</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>侯杰-Willis Hou</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>空运部 (Air Freight)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25-10-24 星期五</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>侯杰-Willis Hou</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>空运部 (Air Freight)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25-10-27 星期一</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
         </is>
       </c>
     </row>
